--- a/лабы/1.4.2/1.4.2.xlsx
+++ b/лабы/1.4.2/1.4.2.xlsx
@@ -27,7 +27,7 @@
     <definedName name="Mпр2">Лист1!$B$4</definedName>
     <definedName name="Mст">Лист1!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1044,12 +1044,11 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
-        <c:axId val="143131776"/>
-        <c:axId val="143133312"/>
+        <c:axId val="103918976"/>
+        <c:axId val="137274496"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="143131776"/>
+        <c:axId val="103918976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1118,12 +1117,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143133312"/>
+        <c:crossAx val="137274496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="143133312"/>
+        <c:axId val="137274496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1178,7 +1177,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143131776"/>
+        <c:crossAx val="103918976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1227,7 +1226,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1548,12 +1547,11 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
-        <c:axId val="143186944"/>
-        <c:axId val="143794944"/>
+        <c:axId val="104039936"/>
+        <c:axId val="104041472"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="143186944"/>
+        <c:axId val="104039936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1622,12 +1620,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143794944"/>
+        <c:crossAx val="104041472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="143794944"/>
+        <c:axId val="104041472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1682,7 +1680,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143186944"/>
+        <c:crossAx val="104039936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1762,7 +1760,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2040,12 +2038,11 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
-        <c:axId val="143849344"/>
-        <c:axId val="143850880"/>
+        <c:axId val="103993728"/>
+        <c:axId val="103995264"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="143849344"/>
+        <c:axId val="103993728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2089,12 +2086,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143850880"/>
+        <c:crossAx val="103995264"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="143850880"/>
+        <c:axId val="103995264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2129,7 +2126,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="143849344"/>
+        <c:crossAx val="103993728"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2156,7 +2153,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2587,12 +2584,11 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
-        <c:axId val="144594432"/>
-        <c:axId val="144596352"/>
+        <c:axId val="104366080"/>
+        <c:axId val="104368000"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="144594432"/>
+        <c:axId val="104366080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2669,12 +2665,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144596352"/>
+        <c:crossAx val="104368000"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="144596352"/>
+        <c:axId val="104368000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2710,7 +2706,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144594432"/>
+        <c:crossAx val="104366080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2730,8 +2726,8 @@
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.82501563477173201"/>
-          <c:y val="0.34318706697459606"/>
-          <c:w val="0.16185115697310798"/>
+          <c:y val="0.34318706697459611"/>
+          <c:w val="0.16185115697310795"/>
           <c:h val="0.20739030023094701"/>
         </c:manualLayout>
       </c:layout>
@@ -2768,7 +2764,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -3299,12 +3295,11 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
-        <c:axId val="144612352"/>
-        <c:axId val="144712448"/>
+        <c:axId val="111142400"/>
+        <c:axId val="111143936"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="144612352"/>
+        <c:axId val="111142400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="30"/>
@@ -3331,12 +3326,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144712448"/>
+        <c:crossAx val="111143936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="144712448"/>
+        <c:axId val="111143936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3371,7 +3366,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="144612352"/>
+        <c:crossAx val="111142400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3419,7 +3414,7 @@
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -3445,7 +3440,7 @@
         <xdr:cNvPr id="5" name="Диаграмма 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2EA60BC4-C983-4D43-86F9-0CAEEE232AC6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EA60BC4-C983-4D43-86F9-0CAEEE232AC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3481,7 +3476,7 @@
         <xdr:cNvPr id="6" name="Диаграмма 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2319BA84-F8DE-4E96-9355-012E36599031}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2319BA84-F8DE-4E96-9355-012E36599031}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3522,7 +3517,7 @@
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3558,7 +3553,7 @@
         <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3594,7 +3589,7 @@
         <xdr:cNvPr id="4" name=" 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3627,7 +3622,7 @@
         <xdr:cNvPr id="4" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3937,7 +3932,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4060,7 +4055,7 @@
         <v>20</v>
       </c>
       <c r="P3" s="1">
-        <f t="shared" ref="P3:P8" si="0">N3/O3</f>
+        <f t="shared" ref="P3:P7" si="0">N3/O3</f>
         <v>1.5820000000000001</v>
       </c>
       <c r="Q3" s="1" t="s">
@@ -4470,7 +4465,7 @@
         <v>20</v>
       </c>
       <c r="T15" s="1">
-        <f t="shared" ref="T15" si="6">R15/S15</f>
+        <f t="shared" ref="T15:T16" si="6">R15/S15</f>
         <v>1.5580000000000001</v>
       </c>
     </row>
@@ -4484,6 +4479,28 @@
       <c r="E16" s="97"/>
       <c r="F16" s="31"/>
       <c r="G16" s="2"/>
+      <c r="N16" s="1">
+        <f>N15*15</f>
+        <v>466.8</v>
+      </c>
+      <c r="O16" s="1">
+        <v>300</v>
+      </c>
+      <c r="P16" s="1">
+        <f t="shared" ref="P16" si="7">N16/O16</f>
+        <v>1.556</v>
+      </c>
+      <c r="R16" s="1">
+        <f>R15*15</f>
+        <v>467.4</v>
+      </c>
+      <c r="S16" s="1">
+        <v>300</v>
+      </c>
+      <c r="T16" s="1">
+        <f t="shared" si="6"/>
+        <v>1.5579999999999998</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15.5">
       <c r="A17" s="2"/>
@@ -4525,15 +4542,15 @@
         <v>2</v>
       </c>
       <c r="C19" s="35">
-        <f t="shared" ref="C19:C35" si="7">(Mполн * L_1 - Mст * Lпр/2 - Mпр2 * Lпр - M_2 * (Lпр + $B19))/M_1</f>
+        <f t="shared" ref="C19:C35" si="8">(Mполн * L_1 - Mст * Lпр/2 - Mпр2 * Lпр - M_2 * (Lпр + $B19))/M_1</f>
         <v>34.135335768796757</v>
       </c>
       <c r="D19" s="36">
-        <f t="shared" ref="D19:D35" si="8">Jполн - Jст</f>
+        <f t="shared" ref="D19:D35" si="9">Jполн - Jст</f>
         <v>0.22187862469485706</v>
       </c>
       <c r="E19" s="37">
-        <f t="shared" ref="E19:E35" si="9">( M_1 *(Lпр  -  $C19)^2 + M_2 * $B19^2)/10000000</f>
+        <f t="shared" ref="E19:E35" si="10">( M_1 *(Lпр  -  $C19)^2 + M_2 * $B19^2)/10000000</f>
         <v>0.10114514243719822</v>
       </c>
       <c r="F19" s="38"/>
@@ -4547,15 +4564,15 @@
         <v>3</v>
       </c>
       <c r="C20" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>33.141829275290263</v>
       </c>
       <c r="D20" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E20" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10973553397300526</v>
       </c>
       <c r="F20" s="42"/>
@@ -4568,15 +4585,15 @@
         <v>4</v>
       </c>
       <c r="C21" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>32.148322781783762</v>
       </c>
       <c r="D21" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E21" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.11891763810621497</v>
       </c>
       <c r="F21" s="42"/>
@@ -4589,15 +4606,15 @@
         <v>5</v>
       </c>
       <c r="C22" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31.154816288277274</v>
       </c>
       <c r="D22" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E22" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.12869145483682715</v>
       </c>
       <c r="F22" s="42"/>
@@ -4610,15 +4627,15 @@
         <v>6</v>
       </c>
       <c r="C23" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>30.161309794770776</v>
       </c>
       <c r="D23" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E23" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13905698416484202</v>
       </c>
       <c r="F23" s="42"/>
@@ -4631,15 +4648,15 @@
         <v>7</v>
       </c>
       <c r="C24" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>29.167803301264289</v>
       </c>
       <c r="D24" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E24" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.15001422609025938</v>
       </c>
       <c r="F24" s="42"/>
@@ -4652,15 +4669,15 @@
         <v>8</v>
       </c>
       <c r="C25" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>28.174296807757791</v>
       </c>
       <c r="D25" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E25" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.16156318061307945</v>
       </c>
       <c r="F25" s="42"/>
@@ -4673,15 +4690,15 @@
         <v>9</v>
       </c>
       <c r="C26" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27.180790314251297</v>
       </c>
       <c r="D26" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E26" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.17370384773330211</v>
       </c>
       <c r="F26" s="42"/>
@@ -4694,15 +4711,15 @@
         <v>10</v>
       </c>
       <c r="C27" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>26.187283820744806</v>
       </c>
       <c r="D27" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E27" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.18643622745092728</v>
       </c>
       <c r="F27" s="42"/>
@@ -4715,15 +4732,15 @@
         <v>11</v>
       </c>
       <c r="C28" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25.193777327238312</v>
       </c>
       <c r="D28" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E28" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.19976031976595515</v>
       </c>
       <c r="F28" s="42"/>
@@ -4736,15 +4753,15 @@
         <v>12</v>
       </c>
       <c r="C29" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>24.200270833731821</v>
       </c>
       <c r="D29" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E29" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.21367612467838554</v>
       </c>
       <c r="F29" s="42"/>
@@ -4757,15 +4774,15 @@
         <v>13</v>
       </c>
       <c r="C30" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>23.206764340225327</v>
       </c>
       <c r="D30" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E30" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.22818364218821857</v>
       </c>
       <c r="F30" s="42"/>
@@ -4778,15 +4795,15 @@
         <v>14</v>
       </c>
       <c r="C31" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>22.213257846718829</v>
       </c>
       <c r="D31" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E31" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.2432828722954542</v>
       </c>
       <c r="F31" s="42"/>
@@ -4799,15 +4816,15 @@
         <v>15</v>
       </c>
       <c r="C32" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>21.219751353212342</v>
       </c>
       <c r="D32" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E32" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.25897381500009231</v>
       </c>
       <c r="F32" s="42"/>
@@ -4820,15 +4837,15 @@
         <v>16</v>
       </c>
       <c r="C33" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20.226244859705844</v>
       </c>
       <c r="D33" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E33" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.27525647030213324</v>
       </c>
       <c r="F33" s="42"/>
@@ -4841,15 +4858,15 @@
         <v>17</v>
       </c>
       <c r="C34" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19.232738366199357</v>
       </c>
       <c r="D34" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E34" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.29213083820157654</v>
       </c>
       <c r="F34" s="42"/>
@@ -4862,15 +4879,15 @@
         <v>18</v>
       </c>
       <c r="C35" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>18.239231872692859</v>
       </c>
       <c r="D35" s="36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E35" s="37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.30959691869842265</v>
       </c>
       <c r="F35" s="42"/>
@@ -4931,15 +4948,15 @@
         <v>11.8</v>
       </c>
       <c r="C40" s="53">
-        <f t="shared" ref="C40:C50" si="10">(Mполн * L_1 - Mст * Lпр/2 - Mпр2 * Lпр - M_2 * (Lпр + $B40))/M_1</f>
+        <f t="shared" ref="C40:C50" si="11">(Mполн * L_1 - Mст * Lпр/2 - Mпр2 * Lпр - M_2 * (Lпр + $B40))/M_1</f>
         <v>24.398972132433116</v>
       </c>
       <c r="D40" s="54">
-        <f t="shared" ref="D40:D50" si="11">Jполн - Jст</f>
+        <f t="shared" ref="D40:D50" si="12">Jполн - Jст</f>
         <v>0.22187862469485706</v>
       </c>
       <c r="E40" s="55">
-        <f t="shared" ref="E40:E50" si="12">( M_1 *(Lпр  -  $C40)^2 + M_2 * $B40^2)/10000000</f>
+        <f t="shared" ref="E40:E50" si="13">( M_1 *(Lпр  -  $C40)^2 + M_2 * $B40^2)/10000000</f>
         <v>0.2108456266881073</v>
       </c>
     </row>
@@ -4950,15 +4967,15 @@
         <v>11.9</v>
       </c>
       <c r="C41" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24.299621483082465</v>
       </c>
       <c r="D41" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E41" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.21225791712025949</v>
       </c>
     </row>
@@ -4969,15 +4986,15 @@
         <v>12</v>
       </c>
       <c r="C42" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24.200270833731821</v>
       </c>
       <c r="D42" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E42" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.21367612467838554</v>
       </c>
       <c r="F42" s="42"/>
@@ -4991,15 +5008,15 @@
         <v>12.100000000000001</v>
       </c>
       <c r="C43" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24.100920184381163</v>
       </c>
       <c r="D43" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E43" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.21510024936248581</v>
       </c>
       <c r="F43" s="42"/>
@@ -5013,15 +5030,15 @@
         <v>12.200000000000001</v>
       </c>
       <c r="C44" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24.001569535030519</v>
       </c>
       <c r="D44" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E44" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.21653029117255998</v>
       </c>
       <c r="F44" s="42"/>
@@ -5035,15 +5052,15 @@
         <v>12.3</v>
       </c>
       <c r="C45" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.902218885679879</v>
       </c>
       <c r="D45" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E45" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2179662501086081</v>
       </c>
       <c r="F45" s="42"/>
@@ -5057,15 +5074,15 @@
         <v>12.4</v>
       </c>
       <c r="C46" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.802868236329218</v>
       </c>
       <c r="D46" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E46" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.21940812617063052</v>
       </c>
       <c r="F46" s="42"/>
@@ -5079,15 +5096,15 @@
         <v>12.5</v>
       </c>
       <c r="C47" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.703517586978574</v>
       </c>
       <c r="D47" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E47" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.2208559193586267</v>
       </c>
       <c r="F47" s="42"/>
@@ -5101,15 +5118,15 @@
         <v>12.600000000000001</v>
       </c>
       <c r="C48" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.604166937627912</v>
       </c>
       <c r="D48" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E48" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.22230962967259721</v>
       </c>
       <c r="F48" s="42"/>
@@ -5123,15 +5140,15 @@
         <v>12.700000000000001</v>
       </c>
       <c r="C49" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.504816288277272</v>
       </c>
       <c r="D49" s="36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E49" s="37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.22376925711254148</v>
       </c>
       <c r="F49" s="42"/>
@@ -5145,15 +5162,15 @@
         <v>12.8</v>
       </c>
       <c r="C50" s="45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.405465638926628</v>
       </c>
       <c r="D50" s="46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22187862469485706</v>
       </c>
       <c r="E50" s="47">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.22523480167845972</v>
       </c>
       <c r="F50" s="42"/>
